--- a/DataSets/Surratt-2025-09/dbkyes4Waldon.xlsx
+++ b/DataSets/Surratt-2025-09/dbkyes4Waldon.xlsx
@@ -1,24 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\ProjectsPapersConferences\Loxahatchee\LoxModelUpdate\39-BoxProject\DataSets\Surratt-2025-09\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D17ABB1-C8B2-40B4-AABD-B07F05162130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="870" windowWidth="28800" windowHeight="14610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$Z$57</definedName>
+  </definedNames>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="jib9V0e6gvA8J8a3dtA6g3C69B3ZhI8Orhso1rAVYqA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="uBgVd/xLSQNQIOTQ+0jFCQygmC5O00XhDfLkzI0VCI4="/>
     </ext>
   </extLst>
 </workbook>
@@ -363,26 +356,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -390,45 +375,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -618,23 +594,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="10" width="8.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
-    <col min="12" max="12" width="10.28515625" customWidth="1"/>
-    <col min="13" max="26" width="8.5703125" customWidth="1"/>
+    <col customWidth="1" min="1" max="10" width="8.63"/>
+    <col customWidth="1" min="11" max="11" width="11.13"/>
+    <col customWidth="1" min="12" max="12" width="10.25"/>
+    <col customWidth="1" min="13" max="26" width="8.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +684,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -740,28 +716,28 @@
         <v>30</v>
       </c>
       <c r="K2" s="2">
-        <v>29434</v>
+        <v>29434.0</v>
       </c>
       <c r="L2" s="2">
-        <v>39100</v>
+        <v>39100.0</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P2" s="1">
-        <v>263630.69799999997</v>
+        <v>263630.698</v>
       </c>
       <c r="Q2" s="1">
         <v>801716.647</v>
       </c>
       <c r="R2" s="1">
-        <v>888822.77099999995</v>
+        <v>888822.771</v>
       </c>
       <c r="S2" s="1">
-        <v>827520.00899999996</v>
+        <v>827520.009</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>32</v>
@@ -770,16 +746,16 @@
         <v>33</v>
       </c>
       <c r="V2" s="1">
-        <v>31</v>
+        <v>31.0</v>
       </c>
       <c r="W2" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X2" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -811,28 +787,28 @@
         <v>30</v>
       </c>
       <c r="K3" s="2">
-        <v>29434</v>
+        <v>29434.0</v>
       </c>
       <c r="L3" s="2">
-        <v>41639</v>
+        <v>41639.0</v>
       </c>
       <c r="M3" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P3" s="1">
-        <v>263536.78100000002</v>
+        <v>263536.781</v>
       </c>
       <c r="Q3" s="1">
-        <v>801616.54599999997</v>
+        <v>801616.546</v>
       </c>
       <c r="R3" s="1">
-        <v>894308.80799999996</v>
+        <v>894308.808</v>
       </c>
       <c r="S3" s="1">
-        <v>822106.58400000003</v>
+        <v>822106.584</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>32</v>
@@ -841,21 +817,21 @@
         <v>33</v>
       </c>
       <c r="V3" s="1">
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="W3" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X3" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1">
-        <v>15023</v>
+        <v>15023.0</v>
       </c>
       <c r="B4" s="1">
-        <v>15023</v>
+        <v>15023.0</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>35</v>
@@ -882,28 +858,28 @@
         <v>38</v>
       </c>
       <c r="K4" s="2">
-        <v>29221</v>
+        <v>29221.0</v>
       </c>
       <c r="L4" s="2">
-        <v>43434</v>
+        <v>43434.0</v>
       </c>
       <c r="M4" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P4" s="1">
-        <v>263536.78100000002</v>
+        <v>263536.781</v>
       </c>
       <c r="Q4" s="1">
-        <v>801616.54599999997</v>
+        <v>801616.546</v>
       </c>
       <c r="R4" s="1">
-        <v>894308.80799999996</v>
+        <v>894308.808</v>
       </c>
       <c r="S4" s="1">
-        <v>822106.58400000003</v>
+        <v>822106.584</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>32</v>
@@ -912,21 +888,21 @@
         <v>33</v>
       </c>
       <c r="V4" s="1">
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="W4" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X4" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="1">
-        <v>90934</v>
+        <v>90934.0</v>
       </c>
       <c r="B5" s="1">
-        <v>90934</v>
+        <v>90934.0</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>39</v>
@@ -953,28 +929,28 @@
         <v>30</v>
       </c>
       <c r="K5" s="2">
-        <v>34256</v>
+        <v>34256.0</v>
       </c>
       <c r="L5" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M5" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P5" s="1">
-        <v>263552.03499999997</v>
+        <v>263552.035</v>
       </c>
       <c r="Q5" s="1">
-        <v>802631.24600000004</v>
+        <v>802631.246</v>
       </c>
       <c r="R5" s="1">
         <v>838503.571</v>
       </c>
       <c r="S5" s="1">
-        <v>823367.96900000004</v>
+        <v>823367.969</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>43</v>
@@ -983,16 +959,16 @@
         <v>33</v>
       </c>
       <c r="V5" s="1">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="W5" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X5" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
@@ -1024,28 +1000,28 @@
         <v>30</v>
       </c>
       <c r="K6" s="2">
-        <v>36344</v>
+        <v>36344.0</v>
       </c>
       <c r="L6" s="2">
-        <v>43616</v>
+        <v>43616.0</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P6" s="1">
-        <v>263552.03499999997</v>
+        <v>263552.035</v>
       </c>
       <c r="Q6" s="1">
-        <v>802631.24600000004</v>
+        <v>802631.246</v>
       </c>
       <c r="R6" s="1">
         <v>838503.571</v>
       </c>
       <c r="S6" s="1">
-        <v>823367.96900000004</v>
+        <v>823367.969</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>43</v>
@@ -1054,16 +1030,16 @@
         <v>33</v>
       </c>
       <c r="V6" s="1">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="W6" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X6" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
@@ -1095,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="K7" s="2">
-        <v>36467</v>
+        <v>36467.0</v>
       </c>
       <c r="L7" s="2">
-        <v>41639</v>
+        <v>41639.0</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>31</v>
@@ -1110,13 +1086,13 @@
         <v>264038.391</v>
       </c>
       <c r="Q7" s="1">
-        <v>802146.77399999998</v>
+        <v>802146.774</v>
       </c>
       <c r="R7" s="1">
         <v>864181.77</v>
       </c>
       <c r="S7" s="1">
-        <v>852402.64399999997</v>
+        <v>852402.644</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>43</v>
@@ -1125,16 +1101,16 @@
         <v>48</v>
       </c>
       <c r="V7" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W7" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X7" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
@@ -1166,13 +1142,13 @@
         <v>30</v>
       </c>
       <c r="K8" s="2">
-        <v>36466</v>
+        <v>36466.0</v>
       </c>
       <c r="L8" s="2">
-        <v>43616</v>
+        <v>43616.0</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>31</v>
@@ -1181,13 +1157,13 @@
         <v>264038.391</v>
       </c>
       <c r="Q8" s="1">
-        <v>802146.77399999998</v>
+        <v>802146.774</v>
       </c>
       <c r="R8" s="1">
         <v>864181.77</v>
       </c>
       <c r="S8" s="1">
-        <v>852402.64399999997</v>
+        <v>852402.644</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>43</v>
@@ -1196,21 +1172,21 @@
         <v>48</v>
       </c>
       <c r="V8" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W8" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X8" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="1">
-        <v>90939</v>
+        <v>90939.0</v>
       </c>
       <c r="B9" s="1">
-        <v>90939</v>
+        <v>90939.0</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>46</v>
@@ -1237,13 +1213,13 @@
         <v>30</v>
       </c>
       <c r="K9" s="2">
-        <v>36466</v>
+        <v>36466.0</v>
       </c>
       <c r="L9" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>31</v>
@@ -1252,13 +1228,13 @@
         <v>264038.391</v>
       </c>
       <c r="Q9" s="1">
-        <v>802146.77399999998</v>
+        <v>802146.774</v>
       </c>
       <c r="R9" s="1">
         <v>864181.77</v>
       </c>
       <c r="S9" s="1">
-        <v>852402.64399999997</v>
+        <v>852402.644</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>43</v>
@@ -1267,16 +1243,16 @@
         <v>48</v>
       </c>
       <c r="V9" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W9" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X9" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>50</v>
       </c>
@@ -1308,16 +1284,16 @@
         <v>30</v>
       </c>
       <c r="K10" s="2">
-        <v>36466</v>
+        <v>36466.0</v>
       </c>
       <c r="L10" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="1">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>31</v>
@@ -1326,13 +1302,13 @@
         <v>264038.391</v>
       </c>
       <c r="Q10" s="1">
-        <v>802146.77399999998</v>
+        <v>802146.774</v>
       </c>
       <c r="R10" s="1">
         <v>864181.77</v>
       </c>
       <c r="S10" s="1">
-        <v>852402.64399999997</v>
+        <v>852402.644</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>43</v>
@@ -1341,16 +1317,16 @@
         <v>48</v>
       </c>
       <c r="V10" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W10" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X10" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
@@ -1382,13 +1358,13 @@
         <v>30</v>
       </c>
       <c r="K11" s="2">
-        <v>36467</v>
+        <v>36467.0</v>
       </c>
       <c r="L11" s="2">
-        <v>41639</v>
+        <v>41639.0</v>
       </c>
       <c r="M11" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>31</v>
@@ -1397,13 +1373,13 @@
         <v>264038.391</v>
       </c>
       <c r="Q11" s="1">
-        <v>802146.77399999998</v>
+        <v>802146.774</v>
       </c>
       <c r="R11" s="1">
         <v>864181.77</v>
       </c>
       <c r="S11" s="1">
-        <v>852402.64399999997</v>
+        <v>852402.644</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>43</v>
@@ -1412,16 +1388,16 @@
         <v>48</v>
       </c>
       <c r="V11" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W11" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X11" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
@@ -1453,13 +1429,13 @@
         <v>30</v>
       </c>
       <c r="K12" s="2">
-        <v>36466</v>
+        <v>36466.0</v>
       </c>
       <c r="L12" s="2">
-        <v>43616</v>
+        <v>43616.0</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>31</v>
@@ -1468,13 +1444,13 @@
         <v>264038.391</v>
       </c>
       <c r="Q12" s="1">
-        <v>802146.77399999998</v>
+        <v>802146.774</v>
       </c>
       <c r="R12" s="1">
         <v>864181.77</v>
       </c>
       <c r="S12" s="1">
-        <v>852402.64399999997</v>
+        <v>852402.644</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>43</v>
@@ -1483,21 +1459,21 @@
         <v>48</v>
       </c>
       <c r="V12" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W12" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X12" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="1">
-        <v>90939</v>
+        <v>90939.0</v>
       </c>
       <c r="B13" s="1">
-        <v>90939</v>
+        <v>90939.0</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>46</v>
@@ -1524,13 +1500,13 @@
         <v>30</v>
       </c>
       <c r="K13" s="2">
-        <v>36466</v>
+        <v>36466.0</v>
       </c>
       <c r="L13" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M13" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>31</v>
@@ -1539,13 +1515,13 @@
         <v>264038.391</v>
       </c>
       <c r="Q13" s="1">
-        <v>802146.77399999998</v>
+        <v>802146.774</v>
       </c>
       <c r="R13" s="1">
         <v>864181.77</v>
       </c>
       <c r="S13" s="1">
-        <v>852402.64399999997</v>
+        <v>852402.644</v>
       </c>
       <c r="T13" s="1" t="s">
         <v>43</v>
@@ -1554,16 +1530,16 @@
         <v>48</v>
       </c>
       <c r="V13" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W13" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X13" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
@@ -1595,28 +1571,28 @@
         <v>30</v>
       </c>
       <c r="K14" s="2">
-        <v>36466</v>
+        <v>36466.0</v>
       </c>
       <c r="L14" s="2">
-        <v>41639</v>
+        <v>41639.0</v>
       </c>
       <c r="M14" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P14" s="1">
-        <v>264032.26400000002</v>
+        <v>264032.264</v>
       </c>
       <c r="Q14" s="1">
-        <v>802248.83200000005</v>
+        <v>802248.832</v>
       </c>
       <c r="R14" s="1">
-        <v>858555.47499999998</v>
+        <v>858555.475</v>
       </c>
       <c r="S14" s="1">
-        <v>851756.31400000001</v>
+        <v>851756.314</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>43</v>
@@ -1625,16 +1601,16 @@
         <v>48</v>
       </c>
       <c r="V14" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W14" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X14" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>55</v>
       </c>
@@ -1666,28 +1642,28 @@
         <v>30</v>
       </c>
       <c r="K15" s="2">
-        <v>36466</v>
+        <v>36466.0</v>
       </c>
       <c r="L15" s="2">
-        <v>43616</v>
+        <v>43616.0</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P15" s="1">
-        <v>264032.26400000002</v>
+        <v>264032.264</v>
       </c>
       <c r="Q15" s="1">
-        <v>802248.83200000005</v>
+        <v>802248.832</v>
       </c>
       <c r="R15" s="1">
-        <v>858555.47499999998</v>
+        <v>858555.475</v>
       </c>
       <c r="S15" s="1">
-        <v>851756.31400000001</v>
+        <v>851756.314</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>43</v>
@@ -1696,21 +1672,21 @@
         <v>48</v>
       </c>
       <c r="V15" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W15" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X15" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="1">
-        <v>90940</v>
+        <v>90940.0</v>
       </c>
       <c r="B16" s="1">
-        <v>90940</v>
+        <v>90940.0</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>53</v>
@@ -1737,28 +1713,28 @@
         <v>30</v>
       </c>
       <c r="K16" s="2">
-        <v>36398</v>
+        <v>36398.0</v>
       </c>
       <c r="L16" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P16" s="1">
-        <v>264032.26400000002</v>
+        <v>264032.264</v>
       </c>
       <c r="Q16" s="1">
-        <v>802248.83200000005</v>
+        <v>802248.832</v>
       </c>
       <c r="R16" s="1">
-        <v>858555.47499999998</v>
+        <v>858555.475</v>
       </c>
       <c r="S16" s="1">
-        <v>851756.31400000001</v>
+        <v>851756.314</v>
       </c>
       <c r="T16" s="1" t="s">
         <v>43</v>
@@ -1767,16 +1743,16 @@
         <v>48</v>
       </c>
       <c r="V16" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W16" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X16" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1808,31 +1784,31 @@
         <v>30</v>
       </c>
       <c r="K17" s="2">
-        <v>36398</v>
+        <v>36398.0</v>
       </c>
       <c r="L17" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M17" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N17" s="1">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P17" s="1">
-        <v>264032.26400000002</v>
+        <v>264032.264</v>
       </c>
       <c r="Q17" s="1">
-        <v>802248.83200000005</v>
+        <v>802248.832</v>
       </c>
       <c r="R17" s="1">
-        <v>858555.47499999998</v>
+        <v>858555.475</v>
       </c>
       <c r="S17" s="1">
-        <v>851756.31400000001</v>
+        <v>851756.314</v>
       </c>
       <c r="T17" s="1" t="s">
         <v>43</v>
@@ -1841,16 +1817,16 @@
         <v>48</v>
       </c>
       <c r="V17" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W17" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X17" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -1882,28 +1858,28 @@
         <v>30</v>
       </c>
       <c r="K18" s="2">
-        <v>36466</v>
+        <v>36466.0</v>
       </c>
       <c r="L18" s="2">
-        <v>41639</v>
+        <v>41639.0</v>
       </c>
       <c r="M18" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P18" s="1">
-        <v>264032.26400000002</v>
+        <v>264032.264</v>
       </c>
       <c r="Q18" s="1">
-        <v>802248.83200000005</v>
+        <v>802248.832</v>
       </c>
       <c r="R18" s="1">
-        <v>858555.47499999998</v>
+        <v>858555.475</v>
       </c>
       <c r="S18" s="1">
-        <v>851756.31400000001</v>
+        <v>851756.314</v>
       </c>
       <c r="T18" s="1" t="s">
         <v>43</v>
@@ -1912,16 +1888,16 @@
         <v>48</v>
       </c>
       <c r="V18" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W18" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X18" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>55</v>
       </c>
@@ -1953,28 +1929,28 @@
         <v>30</v>
       </c>
       <c r="K19" s="2">
-        <v>36466</v>
+        <v>36466.0</v>
       </c>
       <c r="L19" s="2">
-        <v>43616</v>
+        <v>43616.0</v>
       </c>
       <c r="M19" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P19" s="1">
-        <v>264032.26400000002</v>
+        <v>264032.264</v>
       </c>
       <c r="Q19" s="1">
-        <v>802248.83200000005</v>
+        <v>802248.832</v>
       </c>
       <c r="R19" s="1">
-        <v>858555.47499999998</v>
+        <v>858555.475</v>
       </c>
       <c r="S19" s="1">
-        <v>851756.31400000001</v>
+        <v>851756.314</v>
       </c>
       <c r="T19" s="1" t="s">
         <v>43</v>
@@ -1983,21 +1959,21 @@
         <v>48</v>
       </c>
       <c r="V19" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W19" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X19" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="1">
-        <v>90940</v>
+        <v>90940.0</v>
       </c>
       <c r="B20" s="1">
-        <v>90940</v>
+        <v>90940.0</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>53</v>
@@ -2024,28 +2000,28 @@
         <v>30</v>
       </c>
       <c r="K20" s="2">
-        <v>36398</v>
+        <v>36398.0</v>
       </c>
       <c r="L20" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M20" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P20" s="1">
-        <v>264032.26400000002</v>
+        <v>264032.264</v>
       </c>
       <c r="Q20" s="1">
-        <v>802248.83200000005</v>
+        <v>802248.832</v>
       </c>
       <c r="R20" s="1">
-        <v>858555.47499999998</v>
+        <v>858555.475</v>
       </c>
       <c r="S20" s="1">
-        <v>851756.31400000001</v>
+        <v>851756.314</v>
       </c>
       <c r="T20" s="1" t="s">
         <v>43</v>
@@ -2054,21 +2030,21 @@
         <v>48</v>
       </c>
       <c r="V20" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="W20" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X20" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="1">
-        <v>90973</v>
+        <v>90973.0</v>
       </c>
       <c r="B21" s="1">
-        <v>90973</v>
+        <v>90973.0</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>57</v>
@@ -2095,28 +2071,28 @@
         <v>30</v>
       </c>
       <c r="K21" s="2">
-        <v>36685</v>
+        <v>36685.0</v>
       </c>
       <c r="L21" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M21" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P21" s="1">
-        <v>263550.45199999999</v>
+        <v>263550.452</v>
       </c>
       <c r="Q21" s="1">
-        <v>802646.37300000002</v>
+        <v>802646.373</v>
       </c>
       <c r="R21" s="1">
         <v>837131.223</v>
       </c>
       <c r="S21" s="1">
-        <v>823202.09699999995</v>
+        <v>823202.097</v>
       </c>
       <c r="T21" s="1" t="s">
         <v>43</v>
@@ -2125,16 +2101,16 @@
         <v>33</v>
       </c>
       <c r="V21" s="1">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="W21" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X21" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>59</v>
       </c>
@@ -2166,28 +2142,28 @@
         <v>30</v>
       </c>
       <c r="K22" s="2">
-        <v>36714</v>
+        <v>36714.0</v>
       </c>
       <c r="L22" s="2">
-        <v>43616</v>
+        <v>43616.0</v>
       </c>
       <c r="M22" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P22" s="1">
-        <v>263550.45199999999</v>
+        <v>263550.452</v>
       </c>
       <c r="Q22" s="1">
-        <v>802646.37300000002</v>
+        <v>802646.373</v>
       </c>
       <c r="R22" s="1">
         <v>837131.223</v>
       </c>
       <c r="S22" s="1">
-        <v>823202.09699999995</v>
+        <v>823202.097</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>43</v>
@@ -2196,16 +2172,16 @@
         <v>33</v>
       </c>
       <c r="V22" s="1">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="W22" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X22" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>60</v>
       </c>
@@ -2237,13 +2213,13 @@
         <v>30</v>
       </c>
       <c r="K23" s="2">
-        <v>37335</v>
+        <v>37335.0</v>
       </c>
       <c r="L23" s="2">
-        <v>41274</v>
+        <v>41274.0</v>
       </c>
       <c r="M23" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>31</v>
@@ -2252,13 +2228,13 @@
         <v>262812.147</v>
       </c>
       <c r="Q23" s="1">
-        <v>802643.26100000006</v>
+        <v>802643.261</v>
       </c>
       <c r="R23" s="1">
         <v>837612.03</v>
       </c>
       <c r="S23" s="1">
-        <v>776926.45900000003</v>
+        <v>776926.459</v>
       </c>
       <c r="T23" s="1" t="s">
         <v>63</v>
@@ -2267,21 +2243,21 @@
         <v>48</v>
       </c>
       <c r="V23" s="1">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="W23" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X23" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="1">
-        <v>90333</v>
+        <v>90333.0</v>
       </c>
       <c r="B24" s="1">
-        <v>90333</v>
+        <v>90333.0</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>61</v>
@@ -2308,13 +2284,13 @@
         <v>30</v>
       </c>
       <c r="K24" s="2">
-        <v>41214</v>
+        <v>41214.0</v>
       </c>
       <c r="L24" s="2">
-        <v>43616</v>
+        <v>43616.0</v>
       </c>
       <c r="M24" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>31</v>
@@ -2323,13 +2299,13 @@
         <v>262812.147</v>
       </c>
       <c r="Q24" s="1">
-        <v>802643.26100000006</v>
+        <v>802643.261</v>
       </c>
       <c r="R24" s="1">
         <v>837612.03</v>
       </c>
       <c r="S24" s="1">
-        <v>776926.45900000003</v>
+        <v>776926.459</v>
       </c>
       <c r="T24" s="1" t="s">
         <v>63</v>
@@ -2338,21 +2314,21 @@
         <v>48</v>
       </c>
       <c r="V24" s="1">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="W24" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X24" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="1">
-        <v>91012</v>
+        <v>91012.0</v>
       </c>
       <c r="B25" s="1">
-        <v>91012</v>
+        <v>91012.0</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>61</v>
@@ -2379,13 +2355,13 @@
         <v>30</v>
       </c>
       <c r="K25" s="2">
-        <v>37334</v>
+        <v>37334.0</v>
       </c>
       <c r="L25" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M25" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>31</v>
@@ -2394,13 +2370,13 @@
         <v>262812.147</v>
       </c>
       <c r="Q25" s="1">
-        <v>802643.26100000006</v>
+        <v>802643.261</v>
       </c>
       <c r="R25" s="1">
         <v>837612.03</v>
       </c>
       <c r="S25" s="1">
-        <v>776926.45900000003</v>
+        <v>776926.459</v>
       </c>
       <c r="T25" s="1" t="s">
         <v>63</v>
@@ -2409,16 +2385,16 @@
         <v>48</v>
       </c>
       <c r="V25" s="1">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="W25" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X25" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>64</v>
       </c>
@@ -2450,13 +2426,13 @@
         <v>30</v>
       </c>
       <c r="K26" s="2">
-        <v>37334</v>
+        <v>37334.0</v>
       </c>
       <c r="L26" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M26" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>31</v>
@@ -2465,13 +2441,13 @@
         <v>262812.147</v>
       </c>
       <c r="Q26" s="1">
-        <v>802643.26100000006</v>
+        <v>802643.261</v>
       </c>
       <c r="R26" s="1">
         <v>837612.03</v>
       </c>
       <c r="S26" s="1">
-        <v>776926.45900000003</v>
+        <v>776926.459</v>
       </c>
       <c r="T26" s="1" t="s">
         <v>63</v>
@@ -2480,16 +2456,16 @@
         <v>48</v>
       </c>
       <c r="V26" s="1">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="W26" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X26" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
@@ -2521,28 +2497,28 @@
         <v>30</v>
       </c>
       <c r="K27" s="2">
-        <v>36631</v>
+        <v>36631.0</v>
       </c>
       <c r="L27" s="2">
-        <v>39203</v>
+        <v>39203.0</v>
       </c>
       <c r="M27" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P27" s="1">
-        <v>262606.07199999999</v>
+        <v>262606.072</v>
       </c>
       <c r="Q27" s="1">
-        <v>801347.78099999996</v>
+        <v>801347.781</v>
       </c>
       <c r="R27" s="1">
-        <v>908160.95299999998</v>
+        <v>908160.953</v>
       </c>
       <c r="S27" s="1">
-        <v>764561.22699999996</v>
+        <v>764561.227</v>
       </c>
       <c r="T27" s="1" t="s">
         <v>69</v>
@@ -2551,16 +2527,16 @@
         <v>70</v>
       </c>
       <c r="V27" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="W27" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X27" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>71</v>
       </c>
@@ -2592,28 +2568,28 @@
         <v>30</v>
       </c>
       <c r="K28" s="2">
-        <v>37410</v>
+        <v>37410.0</v>
       </c>
       <c r="L28" s="2">
-        <v>43456</v>
+        <v>43456.0</v>
       </c>
       <c r="M28" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P28" s="1">
-        <v>262606.07199999999</v>
+        <v>262606.072</v>
       </c>
       <c r="Q28" s="1">
-        <v>801347.78099999996</v>
+        <v>801347.781</v>
       </c>
       <c r="R28" s="1">
-        <v>908160.95299999998</v>
+        <v>908160.953</v>
       </c>
       <c r="S28" s="1">
-        <v>764561.22699999996</v>
+        <v>764561.227</v>
       </c>
       <c r="T28" s="1" t="s">
         <v>69</v>
@@ -2622,16 +2598,16 @@
         <v>70</v>
       </c>
       <c r="V28" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="W28" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X28" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>72</v>
       </c>
@@ -2663,28 +2639,28 @@
         <v>30</v>
       </c>
       <c r="K29" s="2">
-        <v>37411</v>
+        <v>37411.0</v>
       </c>
       <c r="L29" s="2">
-        <v>43585</v>
+        <v>43585.0</v>
       </c>
       <c r="M29" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P29" s="1">
-        <v>262606.07199999999</v>
+        <v>262606.072</v>
       </c>
       <c r="Q29" s="1">
-        <v>801347.78099999996</v>
+        <v>801347.781</v>
       </c>
       <c r="R29" s="1">
-        <v>908160.95299999998</v>
+        <v>908160.953</v>
       </c>
       <c r="S29" s="1">
-        <v>764561.22699999996</v>
+        <v>764561.227</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>69</v>
@@ -2693,16 +2669,16 @@
         <v>70</v>
       </c>
       <c r="V29" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="W29" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X29" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>73</v>
       </c>
@@ -2734,28 +2710,28 @@
         <v>30</v>
       </c>
       <c r="K30" s="2">
-        <v>39329</v>
+        <v>39329.0</v>
       </c>
       <c r="L30" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M30" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P30" s="1">
-        <v>262606.07199999999</v>
+        <v>262606.072</v>
       </c>
       <c r="Q30" s="1">
-        <v>801347.78099999996</v>
+        <v>801347.781</v>
       </c>
       <c r="R30" s="1">
-        <v>908160.95299999998</v>
+        <v>908160.953</v>
       </c>
       <c r="S30" s="1">
-        <v>764561.22699999996</v>
+        <v>764561.227</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>69</v>
@@ -2764,21 +2740,21 @@
         <v>70</v>
       </c>
       <c r="V30" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="W30" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X30" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="1">
-        <v>91281</v>
+        <v>91281.0</v>
       </c>
       <c r="B31" s="1">
-        <v>91281</v>
+        <v>91281.0</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>67</v>
@@ -2805,28 +2781,28 @@
         <v>30</v>
       </c>
       <c r="K31" s="2">
-        <v>36631</v>
+        <v>36631.0</v>
       </c>
       <c r="L31" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M31" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P31" s="1">
-        <v>262606.07199999999</v>
+        <v>262606.072</v>
       </c>
       <c r="Q31" s="1">
-        <v>801347.78099999996</v>
+        <v>801347.781</v>
       </c>
       <c r="R31" s="1">
-        <v>908160.95299999998</v>
+        <v>908160.953</v>
       </c>
       <c r="S31" s="1">
-        <v>764561.22699999996</v>
+        <v>764561.227</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>69</v>
@@ -2835,16 +2811,16 @@
         <v>70</v>
       </c>
       <c r="V31" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="W31" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X31" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>75</v>
       </c>
@@ -2876,19 +2852,19 @@
         <v>30</v>
       </c>
       <c r="K32" s="2">
-        <v>36631</v>
+        <v>36631.0</v>
       </c>
       <c r="L32" s="2">
-        <v>39281</v>
+        <v>39281.0</v>
       </c>
       <c r="M32" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P32" s="1">
-        <v>262854.38900000002</v>
+        <v>262854.389</v>
       </c>
       <c r="Q32" s="1">
         <v>801317.77</v>
@@ -2897,7 +2873,7 @@
         <v>910786.13</v>
       </c>
       <c r="S32" s="1">
-        <v>781572.95499999996</v>
+        <v>781572.955</v>
       </c>
       <c r="T32" s="1" t="s">
         <v>69</v>
@@ -2906,21 +2882,21 @@
         <v>70</v>
       </c>
       <c r="V32" s="1">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="W32" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X32" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="1">
-        <v>91282</v>
+        <v>91282.0</v>
       </c>
       <c r="B33" s="1">
-        <v>91282</v>
+        <v>91282.0</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>76</v>
@@ -2947,19 +2923,19 @@
         <v>30</v>
       </c>
       <c r="K33" s="2">
-        <v>36630</v>
+        <v>36630.0</v>
       </c>
       <c r="L33" s="2">
-        <v>41996</v>
+        <v>41996.0</v>
       </c>
       <c r="M33" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P33" s="1">
-        <v>262854.38900000002</v>
+        <v>262854.389</v>
       </c>
       <c r="Q33" s="1">
         <v>801317.77</v>
@@ -2968,7 +2944,7 @@
         <v>910786.13</v>
       </c>
       <c r="S33" s="1">
-        <v>781572.95499999996</v>
+        <v>781572.955</v>
       </c>
       <c r="T33" s="1" t="s">
         <v>69</v>
@@ -2977,16 +2953,16 @@
         <v>70</v>
       </c>
       <c r="V33" s="1">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="W33" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X33" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>78</v>
       </c>
@@ -3018,19 +2994,19 @@
         <v>30</v>
       </c>
       <c r="K34" s="2">
-        <v>39290</v>
+        <v>39290.0</v>
       </c>
       <c r="L34" s="2">
-        <v>41996</v>
+        <v>41996.0</v>
       </c>
       <c r="M34" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P34" s="1">
-        <v>262854.38900000002</v>
+        <v>262854.389</v>
       </c>
       <c r="Q34" s="1">
         <v>801317.77</v>
@@ -3039,7 +3015,7 @@
         <v>910786.13</v>
       </c>
       <c r="S34" s="1">
-        <v>781572.95499999996</v>
+        <v>781572.955</v>
       </c>
       <c r="T34" s="1" t="s">
         <v>69</v>
@@ -3048,16 +3024,16 @@
         <v>70</v>
       </c>
       <c r="V34" s="1">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="W34" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X34" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>79</v>
       </c>
@@ -3089,19 +3065,19 @@
         <v>30</v>
       </c>
       <c r="K35" s="2">
-        <v>37410</v>
+        <v>37410.0</v>
       </c>
       <c r="L35" s="2">
-        <v>41996</v>
+        <v>41996.0</v>
       </c>
       <c r="M35" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P35" s="1">
-        <v>262854.38900000002</v>
+        <v>262854.389</v>
       </c>
       <c r="Q35" s="1">
         <v>801317.77</v>
@@ -3110,7 +3086,7 @@
         <v>910786.13</v>
       </c>
       <c r="S35" s="1">
-        <v>781572.95499999996</v>
+        <v>781572.955</v>
       </c>
       <c r="T35" s="1" t="s">
         <v>69</v>
@@ -3119,16 +3095,16 @@
         <v>70</v>
       </c>
       <c r="V35" s="1">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="W35" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X35" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>80</v>
       </c>
@@ -3160,28 +3136,28 @@
         <v>30</v>
       </c>
       <c r="K36" s="2">
-        <v>36631</v>
+        <v>36631.0</v>
       </c>
       <c r="L36" s="2">
-        <v>37529</v>
+        <v>37529.0</v>
       </c>
       <c r="M36" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P36" s="1">
-        <v>263228.94699999999</v>
+        <v>263228.947</v>
       </c>
       <c r="Q36" s="1">
-        <v>801357.95900000003</v>
+        <v>801357.959</v>
       </c>
       <c r="R36" s="1">
-        <v>907004.77899999998</v>
+        <v>907004.779</v>
       </c>
       <c r="S36" s="1">
-        <v>803215.51100000006</v>
+        <v>803215.511</v>
       </c>
       <c r="T36" s="1" t="s">
         <v>69</v>
@@ -3190,16 +3166,16 @@
         <v>70</v>
       </c>
       <c r="V36" s="1">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="W36" s="1">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="X36" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>83</v>
       </c>
@@ -3231,28 +3207,28 @@
         <v>30</v>
       </c>
       <c r="K37" s="2">
-        <v>37411</v>
+        <v>37411.0</v>
       </c>
       <c r="L37" s="2">
-        <v>43455</v>
+        <v>43455.0</v>
       </c>
       <c r="M37" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P37" s="1">
-        <v>263228.94699999999</v>
+        <v>263228.947</v>
       </c>
       <c r="Q37" s="1">
-        <v>801357.95900000003</v>
+        <v>801357.959</v>
       </c>
       <c r="R37" s="1">
-        <v>907004.77899999998</v>
+        <v>907004.779</v>
       </c>
       <c r="S37" s="1">
-        <v>803215.51100000006</v>
+        <v>803215.511</v>
       </c>
       <c r="T37" s="1" t="s">
         <v>69</v>
@@ -3261,21 +3237,21 @@
         <v>70</v>
       </c>
       <c r="V37" s="1">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="W37" s="1">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="X37" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="1">
-        <v>91283</v>
+        <v>91283.0</v>
       </c>
       <c r="B38" s="1">
-        <v>91283</v>
+        <v>91283.0</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>81</v>
@@ -3302,28 +3278,28 @@
         <v>30</v>
       </c>
       <c r="K38" s="2">
-        <v>36630</v>
+        <v>36630.0</v>
       </c>
       <c r="L38" s="2">
-        <v>43456</v>
+        <v>43456.0</v>
       </c>
       <c r="M38" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O38" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P38" s="1">
-        <v>263228.94699999999</v>
+        <v>263228.947</v>
       </c>
       <c r="Q38" s="1">
-        <v>801357.95900000003</v>
+        <v>801357.959</v>
       </c>
       <c r="R38" s="1">
-        <v>907004.77899999998</v>
+        <v>907004.779</v>
       </c>
       <c r="S38" s="1">
-        <v>803215.51100000006</v>
+        <v>803215.511</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>69</v>
@@ -3332,16 +3308,16 @@
         <v>70</v>
       </c>
       <c r="V38" s="1">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="W38" s="1">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="X38" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>84</v>
       </c>
@@ -3373,28 +3349,28 @@
         <v>30</v>
       </c>
       <c r="K39" s="2">
-        <v>37410</v>
+        <v>37410.0</v>
       </c>
       <c r="L39" s="2">
-        <v>43456</v>
+        <v>43456.0</v>
       </c>
       <c r="M39" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O39" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P39" s="1">
-        <v>263228.94699999999</v>
+        <v>263228.947</v>
       </c>
       <c r="Q39" s="1">
-        <v>801357.95900000003</v>
+        <v>801357.959</v>
       </c>
       <c r="R39" s="1">
-        <v>907004.77899999998</v>
+        <v>907004.779</v>
       </c>
       <c r="S39" s="1">
-        <v>803215.51100000006</v>
+        <v>803215.511</v>
       </c>
       <c r="T39" s="1" t="s">
         <v>69</v>
@@ -3403,21 +3379,21 @@
         <v>70</v>
       </c>
       <c r="V39" s="1">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="W39" s="1">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="X39" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="1">
-        <v>91346</v>
+        <v>91346.0</v>
       </c>
       <c r="B40" s="1">
-        <v>91346</v>
+        <v>91346.0</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>85</v>
@@ -3444,13 +3420,13 @@
         <v>30</v>
       </c>
       <c r="K40" s="2">
-        <v>33981</v>
+        <v>33981.0</v>
       </c>
       <c r="L40" s="2">
-        <v>34241</v>
+        <v>34241.0</v>
       </c>
       <c r="M40" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>31</v>
@@ -3459,13 +3435,13 @@
         <v>262135.277</v>
       </c>
       <c r="Q40" s="1">
-        <v>801844.17099999997</v>
+        <v>801844.171</v>
       </c>
       <c r="R40" s="1">
-        <v>881362.61899999995</v>
+        <v>881362.619</v>
       </c>
       <c r="S40" s="1">
-        <v>737064.90300000005</v>
+        <v>737064.903</v>
       </c>
       <c r="T40" s="1" t="s">
         <v>69</v>
@@ -3474,21 +3450,21 @@
         <v>48</v>
       </c>
       <c r="V40" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="W40" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X40" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B41" s="1">
-        <v>3784</v>
+        <v>3784.0</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>85</v>
@@ -3515,13 +3491,13 @@
         <v>30</v>
       </c>
       <c r="K41" s="2">
-        <v>33981</v>
+        <v>33981.0</v>
       </c>
       <c r="L41" s="2">
-        <v>36611</v>
+        <v>36611.0</v>
       </c>
       <c r="M41" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>31</v>
@@ -3530,13 +3506,13 @@
         <v>262135.277</v>
       </c>
       <c r="Q41" s="1">
-        <v>801844.17099999997</v>
+        <v>801844.171</v>
       </c>
       <c r="R41" s="1">
-        <v>881362.61899999995</v>
+        <v>881362.619</v>
       </c>
       <c r="S41" s="1">
-        <v>737064.90300000005</v>
+        <v>737064.903</v>
       </c>
       <c r="T41" s="1" t="s">
         <v>69</v>
@@ -3545,16 +3521,16 @@
         <v>48</v>
       </c>
       <c r="V41" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="W41" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X41" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>88</v>
       </c>
@@ -3586,13 +3562,13 @@
         <v>30</v>
       </c>
       <c r="K42" s="2">
-        <v>26785</v>
+        <v>26785.0</v>
       </c>
       <c r="L42" s="2">
-        <v>43585</v>
+        <v>43585.0</v>
       </c>
       <c r="M42" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>31</v>
@@ -3601,13 +3577,13 @@
         <v>262135.277</v>
       </c>
       <c r="Q42" s="1">
-        <v>801844.17099999997</v>
+        <v>801844.171</v>
       </c>
       <c r="R42" s="1">
-        <v>881362.61899999995</v>
+        <v>881362.619</v>
       </c>
       <c r="S42" s="1">
-        <v>737064.90300000005</v>
+        <v>737064.903</v>
       </c>
       <c r="T42" s="1" t="s">
         <v>69</v>
@@ -3616,21 +3592,21 @@
         <v>48</v>
       </c>
       <c r="V42" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="W42" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X42" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="1">
-        <v>15261</v>
+        <v>15261.0</v>
       </c>
       <c r="B43" s="1">
-        <v>15261</v>
+        <v>15261.0</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>85</v>
@@ -3657,13 +3633,13 @@
         <v>89</v>
       </c>
       <c r="K43" s="2">
-        <v>26785</v>
+        <v>26785.0</v>
       </c>
       <c r="L43" s="2">
-        <v>43650</v>
+        <v>43650.0</v>
       </c>
       <c r="M43" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>31</v>
@@ -3672,13 +3648,13 @@
         <v>262135.277</v>
       </c>
       <c r="Q43" s="1">
-        <v>801844.17099999997</v>
+        <v>801844.171</v>
       </c>
       <c r="R43" s="1">
-        <v>881362.61899999995</v>
+        <v>881362.619</v>
       </c>
       <c r="S43" s="1">
-        <v>737064.90300000005</v>
+        <v>737064.903</v>
       </c>
       <c r="T43" s="1" t="s">
         <v>69</v>
@@ -3687,21 +3663,21 @@
         <v>48</v>
       </c>
       <c r="V43" s="1">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="W43" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X43" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B44" s="1">
-        <v>3796</v>
+        <v>3796.0</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>91</v>
@@ -3728,22 +3704,22 @@
         <v>30</v>
       </c>
       <c r="K44" s="2">
-        <v>35246</v>
+        <v>35246.0</v>
       </c>
       <c r="L44" s="2">
-        <v>36611</v>
+        <v>36611.0</v>
       </c>
       <c r="M44" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P44" s="1">
-        <v>262218.27799999999</v>
+        <v>262218.278</v>
       </c>
       <c r="Q44" s="1">
-        <v>802108.17599999998</v>
+        <v>802108.176</v>
       </c>
       <c r="R44" s="1">
         <v>868241.97</v>
@@ -3758,16 +3734,16 @@
         <v>48</v>
       </c>
       <c r="V44" s="1">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="W44" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X44" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>93</v>
       </c>
@@ -3799,22 +3775,22 @@
         <v>30</v>
       </c>
       <c r="K45" s="2">
-        <v>35691</v>
+        <v>35691.0</v>
       </c>
       <c r="L45" s="2">
-        <v>40117</v>
+        <v>40117.0</v>
       </c>
       <c r="M45" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P45" s="1">
-        <v>262218.27799999999</v>
+        <v>262218.278</v>
       </c>
       <c r="Q45" s="1">
-        <v>802108.17599999998</v>
+        <v>802108.176</v>
       </c>
       <c r="R45" s="1">
         <v>868241.97</v>
@@ -3829,21 +3805,21 @@
         <v>48</v>
       </c>
       <c r="V45" s="1">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="W45" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X45" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="1">
-        <v>91347</v>
+        <v>91347.0</v>
       </c>
       <c r="B46" s="1">
-        <v>91347</v>
+        <v>91347.0</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>91</v>
@@ -3870,22 +3846,22 @@
         <v>30</v>
       </c>
       <c r="K46" s="2">
-        <v>35691</v>
+        <v>35691.0</v>
       </c>
       <c r="L46" s="2">
-        <v>40343</v>
+        <v>40343.0</v>
       </c>
       <c r="M46" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P46" s="1">
-        <v>262218.27799999999</v>
+        <v>262218.278</v>
       </c>
       <c r="Q46" s="1">
-        <v>802108.17599999998</v>
+        <v>802108.176</v>
       </c>
       <c r="R46" s="1">
         <v>868241.97</v>
@@ -3900,16 +3876,16 @@
         <v>48</v>
       </c>
       <c r="V46" s="1">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="W46" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X46" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>94</v>
       </c>
@@ -3941,22 +3917,22 @@
         <v>30</v>
       </c>
       <c r="K47" s="2">
-        <v>26785</v>
+        <v>26785.0</v>
       </c>
       <c r="L47" s="2">
-        <v>43585</v>
+        <v>43585.0</v>
       </c>
       <c r="M47" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P47" s="1">
-        <v>262218.27799999999</v>
+        <v>262218.278</v>
       </c>
       <c r="Q47" s="1">
-        <v>802108.17599999998</v>
+        <v>802108.176</v>
       </c>
       <c r="R47" s="1">
         <v>868241.97</v>
@@ -3971,21 +3947,21 @@
         <v>48</v>
       </c>
       <c r="V47" s="1">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="W47" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X47" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="1">
-        <v>15262</v>
+        <v>15262.0</v>
       </c>
       <c r="B48" s="1">
-        <v>15262</v>
+        <v>15262.0</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>91</v>
@@ -4012,22 +3988,22 @@
         <v>89</v>
       </c>
       <c r="K48" s="2">
-        <v>26785</v>
+        <v>26785.0</v>
       </c>
       <c r="L48" s="2">
-        <v>43650</v>
+        <v>43650.0</v>
       </c>
       <c r="M48" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P48" s="1">
-        <v>262218.27799999999</v>
+        <v>262218.278</v>
       </c>
       <c r="Q48" s="1">
-        <v>802108.17599999998</v>
+        <v>802108.176</v>
       </c>
       <c r="R48" s="1">
         <v>868241.97</v>
@@ -4042,21 +4018,21 @@
         <v>48</v>
       </c>
       <c r="V48" s="1">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="W48" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X48" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B49" s="1">
-        <v>3790</v>
+        <v>3790.0</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>96</v>
@@ -4083,28 +4059,28 @@
         <v>30</v>
       </c>
       <c r="K49" s="2">
-        <v>34819</v>
+        <v>34819.0</v>
       </c>
       <c r="L49" s="2">
-        <v>36611</v>
+        <v>36611.0</v>
       </c>
       <c r="M49" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P49" s="1">
-        <v>262319.27399999998</v>
+        <v>262319.274</v>
       </c>
       <c r="Q49" s="1">
-        <v>802254.17599999998</v>
+        <v>802254.176</v>
       </c>
       <c r="R49" s="1">
-        <v>858605.56299999997</v>
+        <v>858605.563</v>
       </c>
       <c r="S49" s="1">
-        <v>747468.18799999997</v>
+        <v>747468.188</v>
       </c>
       <c r="T49" s="1" t="s">
         <v>69</v>
@@ -4113,16 +4089,16 @@
         <v>48</v>
       </c>
       <c r="V49" s="1">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="W49" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X49" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
@@ -4154,28 +4130,28 @@
         <v>30</v>
       </c>
       <c r="K50" s="2">
-        <v>26785</v>
+        <v>26785.0</v>
       </c>
       <c r="L50" s="2">
-        <v>43585</v>
+        <v>43585.0</v>
       </c>
       <c r="M50" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P50" s="1">
-        <v>262319.27399999998</v>
+        <v>262319.274</v>
       </c>
       <c r="Q50" s="1">
-        <v>802254.17599999998</v>
+        <v>802254.176</v>
       </c>
       <c r="R50" s="1">
-        <v>858605.56299999997</v>
+        <v>858605.563</v>
       </c>
       <c r="S50" s="1">
-        <v>747468.18799999997</v>
+        <v>747468.188</v>
       </c>
       <c r="T50" s="1" t="s">
         <v>69</v>
@@ -4184,21 +4160,21 @@
         <v>48</v>
       </c>
       <c r="V50" s="1">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="W50" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X50" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="1">
-        <v>15263</v>
+        <v>15263.0</v>
       </c>
       <c r="B51" s="1">
-        <v>15263</v>
+        <v>15263.0</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>96</v>
@@ -4225,28 +4201,28 @@
         <v>89</v>
       </c>
       <c r="K51" s="2">
-        <v>26785</v>
+        <v>26785.0</v>
       </c>
       <c r="L51" s="2">
-        <v>43650</v>
+        <v>43650.0</v>
       </c>
       <c r="M51" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P51" s="1">
-        <v>262319.27399999998</v>
+        <v>262319.274</v>
       </c>
       <c r="Q51" s="1">
-        <v>802254.17599999998</v>
+        <v>802254.176</v>
       </c>
       <c r="R51" s="1">
-        <v>858605.56299999997</v>
+        <v>858605.563</v>
       </c>
       <c r="S51" s="1">
-        <v>747468.18799999997</v>
+        <v>747468.188</v>
       </c>
       <c r="T51" s="1" t="s">
         <v>69</v>
@@ -4255,21 +4231,21 @@
         <v>48</v>
       </c>
       <c r="V51" s="1">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="W51" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X51" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="1">
-        <v>91348</v>
+        <v>91348.0</v>
       </c>
       <c r="B52" s="1">
-        <v>91348</v>
+        <v>91348.0</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>96</v>
@@ -4296,22 +4272,22 @@
         <v>30</v>
       </c>
       <c r="M52" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P52" s="1">
-        <v>262319.27399999998</v>
+        <v>262319.274</v>
       </c>
       <c r="Q52" s="1">
-        <v>802254.17599999998</v>
+        <v>802254.176</v>
       </c>
       <c r="R52" s="1">
-        <v>858605.56299999997</v>
+        <v>858605.563</v>
       </c>
       <c r="S52" s="1">
-        <v>747468.18799999997</v>
+        <v>747468.188</v>
       </c>
       <c r="T52" s="1" t="s">
         <v>69</v>
@@ -4320,21 +4296,21 @@
         <v>48</v>
       </c>
       <c r="V52" s="1">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="W52" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X52" s="1">
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
-    <row r="53" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="1">
-        <v>91517</v>
+        <v>91517.0</v>
       </c>
       <c r="B53" s="1">
-        <v>91517</v>
+        <v>91517.0</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>99</v>
@@ -4361,13 +4337,13 @@
         <v>30</v>
       </c>
       <c r="K53" s="2">
-        <v>38256</v>
+        <v>38256.0</v>
       </c>
       <c r="L53" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M53" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>31</v>
@@ -4376,13 +4352,13 @@
         <v>263732.23</v>
       </c>
       <c r="Q53" s="1">
-        <v>801904.12100000004</v>
+        <v>801904.121</v>
       </c>
       <c r="R53" s="1">
-        <v>879036.47100000002</v>
+        <v>879036.471</v>
       </c>
       <c r="S53" s="1">
-        <v>833681.59100000001</v>
+        <v>833681.591</v>
       </c>
       <c r="T53" s="1" t="s">
         <v>101</v>
@@ -4391,21 +4367,21 @@
         <v>33</v>
       </c>
       <c r="V53" s="1">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="W53" s="1">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="X53" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="1">
-        <v>91598</v>
+        <v>91598.0</v>
       </c>
       <c r="B54" s="1">
-        <v>91598</v>
+        <v>91598.0</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>102</v>
@@ -4432,28 +4408,28 @@
         <v>30</v>
       </c>
       <c r="K54" s="2">
-        <v>28857</v>
+        <v>28857.0</v>
       </c>
       <c r="L54" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M54" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P54" s="1">
-        <v>262120.64499999999</v>
+        <v>262120.645</v>
       </c>
       <c r="Q54" s="1">
-        <v>801751.56900000002</v>
+        <v>801751.569</v>
       </c>
       <c r="R54" s="1">
-        <v>886157.11699999997</v>
+        <v>886157.117</v>
       </c>
       <c r="S54" s="1">
-        <v>735614.81400000001</v>
+        <v>735614.814</v>
       </c>
       <c r="T54" s="1" t="s">
         <v>69</v>
@@ -4462,21 +4438,21 @@
         <v>48</v>
       </c>
       <c r="V54" s="1">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="W54" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X54" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="55" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B55" s="1">
-        <v>6733</v>
+        <v>6733.0</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>102</v>
@@ -4503,28 +4479,28 @@
         <v>30</v>
       </c>
       <c r="K55" s="2">
-        <v>31198</v>
+        <v>31198.0</v>
       </c>
       <c r="L55" s="2">
-        <v>43649</v>
+        <v>43649.0</v>
       </c>
       <c r="M55" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P55" s="1">
-        <v>262120.64499999999</v>
+        <v>262120.645</v>
       </c>
       <c r="Q55" s="1">
-        <v>801751.56900000002</v>
+        <v>801751.569</v>
       </c>
       <c r="R55" s="1">
-        <v>886157.11699999997</v>
+        <v>886157.117</v>
       </c>
       <c r="S55" s="1">
-        <v>735614.81400000001</v>
+        <v>735614.814</v>
       </c>
       <c r="T55" s="1" t="s">
         <v>69</v>
@@ -4533,21 +4509,21 @@
         <v>48</v>
       </c>
       <c r="V55" s="1">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="W55" s="1">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="X55" s="1">
-        <v>41</v>
+        <v>41.0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="1">
-        <v>91663</v>
+        <v>91663.0</v>
       </c>
       <c r="B56" s="1">
-        <v>91663</v>
+        <v>91663.0</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>105</v>
@@ -4574,13 +4550,13 @@
         <v>30</v>
       </c>
       <c r="K56" s="2">
-        <v>30683</v>
+        <v>30683.0</v>
       </c>
       <c r="L56" s="2">
-        <v>43858</v>
+        <v>43858.0</v>
       </c>
       <c r="M56" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>31</v>
@@ -4589,10 +4565,10 @@
         <v>262818.73</v>
       </c>
       <c r="Q56" s="1">
-        <v>802644.93900000001</v>
+        <v>802644.939</v>
       </c>
       <c r="R56" s="1">
-        <v>837458.43099999998</v>
+        <v>837458.431</v>
       </c>
       <c r="S56" s="1">
         <v>777592.147</v>
@@ -4604,21 +4580,21 @@
         <v>33</v>
       </c>
       <c r="V56" s="1">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="W56" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X56" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="1">
-        <v>91349</v>
+        <v>91349.0</v>
       </c>
       <c r="B57" s="1">
-        <v>91349</v>
+        <v>91349.0</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>108</v>
@@ -4645,13 +4621,13 @@
         <v>30</v>
       </c>
       <c r="K57" s="2">
-        <v>31097</v>
+        <v>31097.0</v>
       </c>
       <c r="L57" s="2">
-        <v>38579</v>
+        <v>38579.0</v>
       </c>
       <c r="M57" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>31</v>
@@ -4663,10 +4639,10 @@
         <v>802629.571</v>
       </c>
       <c r="R57" s="1">
-        <v>838865.18299999996</v>
+        <v>838865.183</v>
       </c>
       <c r="S57" s="1">
-        <v>775252.15500000003</v>
+        <v>775252.155</v>
       </c>
       <c r="T57" s="1" t="s">
         <v>69</v>
@@ -4675,960 +4651,963 @@
         <v>70</v>
       </c>
       <c r="V57" s="1">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="W57" s="1">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="X57" s="1">
-        <v>39</v>
+        <v>39.0</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
+    <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
+    <row r="996" ht="14.25" customHeight="1"/>
+    <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
+    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <autoFilter ref="$A$1:$Z$57"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>